--- a/output/graficos_regionales_indicadores/plot_regional_grupos_e_rezjov_a_2018_los_lagos.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_grupos_e_rezjov_a_2018_los_lagos.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30 04:08</t>
+    <t xml:space="preserve">2026-10-05 06:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
